--- a/reports/播客监控日报_2026-03-16.xlsx
+++ b/reports/播客监控日报_2026-03-16.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日监控数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="每日监控数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -521,80 +521,76 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>大方谈钱</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>华夏基金</t>
-        </is>
-      </c>
+          <t>无人知晓</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="3" t="n">
-        <v>173109</v>
+        <v>1567662</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>首届红火播客节科技场：奇点临近，咱能跟上科技浪潮么？</t>
+          <t>E45 孟岩对话李继刚：人何以自处</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>371893</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1:10:26</t>
+          <t>3:26:38</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:20</t>
+          <t>2026-03-16 22:28:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>厚雪长波</t>
+          <t>商业就是这样</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>雪球财富</t>
+          <t>第一财经</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>121344</v>
+        <v>732138</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>AI时代，文科生要触底反弹了？</t>
+          <t>商业小样35 | 霍尔木兹海峡上的特殊保险</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -604,177 +600,169 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>21686</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>1:18:08</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:22:07</t>
+          <t>2026-03-16 22:27:58</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>中欧基金</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>中欧基金</t>
-        </is>
-      </c>
+          <t>面基</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="3" t="n">
-        <v>77288</v>
+        <v>529818</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46.HALO交易爆火：当AI狂奔，市场又开始拥抱“老派”资产</t>
+          <t>站在美股之巅，满眼山雨欲来</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>77883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>595</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>849</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26:25</t>
+          <t>1:27:26</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:21</t>
+          <t>2026-03-16 22:28:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>和盘托出</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>蚂蚁财富</t>
-        </is>
-      </c>
+          <t>起朱楼宴宾客</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="3" t="n">
-        <v>49519</v>
+        <v>355565</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>关于马斯克精心布局，终于把"奇点年"召唤到眼前，这件大事</t>
+          <t>159.算法的六副面孔：它是如何从处理数据，变成定义我们是谁的</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>28851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>358</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1:12:04</t>
+          <t>1:09:19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:22:05</t>
+          <t>2026-03-16 22:28:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>有富同享</t>
+          <t>大方谈钱</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>富国基金</t>
+          <t>华夏基金</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37878</v>
+        <v>173344</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>一周富盘 | “养龙虾”爆火刷屏！头部大厂纷纷入局，AI智能体热潮下，基金该怎么布局？</t>
+          <t>首届红火播客节科技场：奇点临近，咱能跟上科技浪潮么？</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -784,72 +772,72 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>1:10:26</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:23</t>
+          <t>2026-03-16 22:27:01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>人间钱话</t>
+          <t>中金研究院</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>天弘基金</t>
+          <t>中金公司</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>26905</v>
+        <v>145180</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>E35 美伊冲突全球动荡，如何防止钱包烧毁？</t>
+          <t>episode 49｜中金机器人播客 跨维智能贾奎：物理AI、世界模型与具身智能的商业化路径</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -859,402 +847,386 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33:36</t>
+          <t>1:24:21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:27</t>
+          <t>2026-03-16 22:27:52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>泰度Voice</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>华泰证券</t>
-        </is>
-      </c>
+          <t>三点下班</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="3" t="n">
-        <v>22730</v>
+        <v>141245</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>S3E11 | 超越传统“因子工厂”：AGI开启量化投资新时代</t>
+          <t>如何应对下一次危机--附方法论和检查清单</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>105</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1:00:39</t>
+          <t>56:21</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:22:03</t>
+          <t>2026-03-16 22:28:05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>深度求真</t>
+          <t>厚雪长波</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>大成基金</t>
+          <t>雪球财富</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>20514</v>
+        <v>121870</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18.Seedance出炉，AI视频革命与科技投资新范式</t>
+          <t>AI时代，文科生要触底反弹了？</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44:50</t>
+          <t>1:18:08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:29</t>
+          <t>2026-03-16 22:27:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>话中有金</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>中金资管</t>
-        </is>
-      </c>
+          <t>投资ABC｜掌握投资中那些绕不开的知识</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="3" t="n">
-        <v>8932</v>
+        <v>94077</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>EP135 对话中金公司食品饮料行业首席分析师：当“反向过年”遇上“下沉消费”</t>
+          <t>低利率时代，我的定期存款到期了，这笔钱该怎么办？｜我问陈博士 14</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59:51</t>
+          <t>47:21</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:22:01</t>
+          <t>2026-03-16 22:27:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>德邦基金财经列车</t>
+          <t>中欧基金</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>德邦基金</t>
+          <t>中欧基金</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>8449</v>
+        <v>77938</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>309.全球游客涌向中国春节：一场文化与旅游的双向奔赴</t>
+          <t>46.HALO交易爆火：当AI狂奔，市场又开始拥抱“老派”资产</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5:56</t>
+          <t>26:25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:39</t>
+          <t>2026-03-16 22:27:02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>随基漫步 Random Walk</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>兴全基金</t>
-        </is>
-      </c>
+          <t>钱粮胡同FM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="3" t="n">
-        <v>6913</v>
+        <v>74605</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>OpenClaw爆火后，AI发展的2个重点方向</t>
+          <t>318.伊朗的昨天</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>130</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55:15</t>
+          <t>1:54:25</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:57</t>
+          <t>2026-03-16 22:28:10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>茶水间经济学</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>易方达基金</t>
-        </is>
-      </c>
+          <t>十分吸引</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="3" t="n">
-        <v>6833</v>
+        <v>69490</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>对话三点下班浩哥：他说感谢股市改写了他的人生</t>
+          <t>Vol.59 当"失去的30年"叙事终结：我们该如何看待今天的日本？</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>168</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1:42:13</t>
+          <t>1:11:36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:49</t>
+          <t>2026-03-16 22:28:09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>泰客Talk</t>
+          <t>和盘托出</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>国泰基金</t>
+          <t>蚂蚁财富</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>6275</v>
+        <v>49549</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Vol 27 Z世代的新年消费回忆录</t>
+          <t>关于马斯克精心布局，终于把"奇点年"召唤到眼前，这件大事</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1264,357 +1236,349 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>53:31</t>
+          <t>1:12:04</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:47</t>
+          <t>2026-03-16 22:27:46</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>时间嘉讲</t>
+          <t>有富同享</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>嘉实基金</t>
+          <t>富国基金</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5391</v>
+        <v>38107</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Ep10.当“一盒内存条=一套房”：这轮半导体行情谁在定价？</t>
+          <t>一周富盘 | “养龙虾”爆火刷屏！头部大厂纷纷入局，AI智能体热潮下，基金该怎么布局？</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26180</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1:20:43</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:45</t>
+          <t>2026-03-16 22:27:04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>莫问钱程</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>银华基金</t>
-        </is>
-      </c>
+          <t>The Wanderers 流浪者</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="3" t="n">
-        <v>4475</v>
+        <v>32127</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>养娃这条路，做好财务规划能省多少弯路？</t>
+          <t>2028智能危机：人类经济体会崩溃吗？</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>128</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>211</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1:12:50</t>
+          <t>1:13:53</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:51</t>
+          <t>2026-03-16 22:28:06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>财话连篇</t>
+          <t>人间钱话</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>易方达基金</t>
+          <t>天弘基金</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3817</v>
+        <v>26906</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Vol.18 | 越南市场为何快速上涨？——基金经理越南调研感受</t>
+          <t>E35 美伊冲突全球动荡，如何防止钱包烧毁？</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25:02</t>
+          <t>33:36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:53</t>
+          <t>2026-03-16 22:27:08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>养基方程式</t>
+          <t>泰度Voice</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>广发基金</t>
+          <t>华泰证券</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>3297</v>
+        <v>22734</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港股科技风起，未来路在何方？| 串台「自由进度条」</t>
+          <t>S3E11 | 超越传统“因子工厂”：AGI开启量化投资新时代</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>55:16</t>
+          <t>1:00:39</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:31</t>
+          <t>2026-03-16 22:27:44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>钱途规划局</t>
+          <t>深度求真</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>汇添富基金</t>
+          <t>大成基金</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1983</v>
+        <v>20518</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>E20“宠物理财”小课堂：养毛孩子，怎样花钱不心疼？</t>
+          <t>18.Seedance出炉，AI视频革命与科技投资新范式</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>309</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>44:50</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:55</t>
+          <t>2026-03-16 22:27:10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>好朋友的直播间</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>中泰资管</t>
-        </is>
-      </c>
+          <t>燕妮聊基金</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="3" t="n">
-        <v>1597</v>
+        <v>17298</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>E33.田瑀｜研究不必设限，结论宁缺毋滥</t>
+          <t>86、往期好播客大推荐</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1624,127 +1588,127 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>32:01</t>
+          <t>43:43</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:37</t>
+          <t>2026-03-16 22:28:12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>投资心得·基金聊天局</t>
+          <t>话中有金</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>国投瑞银基金</t>
+          <t>中金资管</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1493</v>
+        <v>8943</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>EP9.别内耗了，允许自己“知行不合一”</t>
+          <t>EP135 对话中金公司食品饮料行业首席分析师：当“反向过年”遇上“下沉消费”</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1:10:07</t>
+          <t>59:51</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:41</t>
+          <t>2026-03-16 22:27:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>与财同行</t>
+          <t>德邦基金财经列车</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>财通基金</t>
+          <t>德邦基金</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1305</v>
+        <v>8470</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>一线基金经理闭门分享：AI、有色、出海……2026年的钱往哪里投？</t>
+          <t>310.一文看懂电力产业：普通投资者必知的行业核心逻辑</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1754,177 +1718,177 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1:29:38</t>
+          <t>3:08</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:25</t>
+          <t>2026-03-16 22:27:21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>鹏然心动</t>
+          <t>随基漫步 Random Walk</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>鹏华基金</t>
+          <t>兴全基金</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>736</v>
+        <v>6950</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Vol 3：新消费浪潮，Z世代用"情绪货币"改写"商业规则"？|元气消费局</t>
+          <t>OpenClaw爆火后，AI发展的2个重点方向</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>54:38</t>
+          <t>55:15</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:59</t>
+          <t>2026-03-16 22:27:38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>基金经理一周论市</t>
+          <t>茶水间经济学</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>银华基金</t>
+          <t>易方达基金</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>305</v>
+        <v>6838</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Vol 53：银华王丽敏：“周期搭台，成长唱戏”或是未来一段时间A股的主旋律</t>
+          <t>对话三点下班浩哥：他说感谢股市改写了他的人生</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2:01</t>
+          <t>1:42:13</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:33</t>
+          <t>2026-03-16 22:27:30</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>好朋友</t>
+          <t>泰客Talk</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>中泰资管</t>
+          <t>国泰基金</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>51</v>
+        <v>6277</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Vol.5 不上班的日子，跑步、做饭、好好生活</t>
+          <t>Vol 27 Z世代的新年消费回忆录</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1934,87 +1898,899 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>158</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>215</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1:00:18</t>
+          <t>53:31</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:21:35</t>
+          <t>2026-03-16 22:27:28</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>时间嘉讲</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>嘉实基金</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5397</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Ep10.当“一盒内存条=一套房”：这轮半导体行情谁在定价？</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>26286</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1:20:43</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>莫问钱程</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>银华基金</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>4478</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>养娃这条路，做好财务规划能省多少弯路？</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>5354</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1:12:50</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>财话连篇</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>易方达基金</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>3816</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Vol.18 | 越南市场为何快速上涨？——基金经理越南调研感受</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4694</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>25:02</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>养基方程式</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>广发基金</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>3297</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>港股科技风起，未来路在何方？| 串台「自由进度条」</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>55:16</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>钱途规划局</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>汇添富基金</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>E20“宠物理财”小课堂：养毛孩子，怎样花钱不心疼？</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>好朋友的直播间</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>中泰资管</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1598</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>E33.田瑀｜研究不必设限，结论宁缺毋滥</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>32:01</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>投资心得·基金聊天局</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>国投瑞银基金</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1494</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>EP9.别内耗了，允许自己“知行不合一”</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1:10:07</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>与财同行</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>财通基金</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1307</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>一线基金经理闭门分享：AI、有色、出海……2026年的钱往哪里投？</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>1:29:38</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>鹏然心动</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>鹏华基金</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>739</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Vol 3：新消费浪潮，Z世代用"情绪货币"改写"商业规则"？|元气消费局</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>54:38</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>对话金融人</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>广发证券</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>481</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>解盘一刻</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>华夏基金</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>A股开年连跌三周，春节行情还能期待吗？0122</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>基金经理一周论市</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>银华基金</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>305</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Vol 53：银华王丽敏：“周期搭台，成长唱戏”或是未来一段时间A股的主旋律</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>2:01</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>好朋友</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>中泰资管</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Vol.5 不上班的日子，跑步、做饭、好好生活</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>1:00:18</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>投资心法</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>国投瑞银基金</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C39" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>0010 段永平《波士堂》访谈：敢为天下后</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>19:39</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-16 03:21:43</t>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:27:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>听懂掌声</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:28:14</t>
         </is>
       </c>
     </row>
